--- a/meta/2-3-2-a.xlsx
+++ b/meta/2-3-2-a.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33565E3F-F5AC-4592-B42F-66BA393C836C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28665" windowHeight="11760"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -103,9 +104,8 @@
     <t>2.3.2.a «Доля произведенной продукции сельскохозяйственными кооперативами в общем объеме произведенной продукции»</t>
   </si>
   <si>
-    <t xml:space="preserve">Национальный cтатистический комитет
-Кыргызской Республики отдел статистики сельского хозяйства
-</t>
+    <t>Национальный cтатистический комитет
+Кыргызской Республики отдел статистики сельского хозяйства</t>
   </si>
   <si>
     <t>Мурсабекова Г.Т.</t>
@@ -123,7 +123,7 @@
     <t>Определении доли произведенной продукции сельскохозяйственными кооперативами в общем объеме произведенной продукции, в %</t>
   </si>
   <si>
-    <t xml:space="preserve">    Национальной стратегией устойчивого развития Кыргызской Республики, предусмотрены следующие меры в целях развития кооперации: использование механизма государственной помощи, при котором она будет увязана с показателями эффективности деятельности сельского товаропроизводителя - получателя помощи; при государственной поддержке аграрного сектора предпочтение будет отдаваться сельхозкооперативам, которые гарантируют сохранение уровня, а в перспективе - рост объемов производства сельскохозяйственной продукции, создание рабочих мест. При этом все формы кооперации будут иметь преимущественное право на государственную поддержку.
+    <t xml:space="preserve">   Национальной стратегией устойчивого развития Кыргызской Республики, предусмотрены следующие меры в целях развития кооперации: использование механизма государственной помощи, при котором она будет увязана с показателями эффективности деятельности сельского товаропроизводителя - получателя помощи; при государственной поддержке аграрного сектора предпочтение будет отдаваться сельхозкооперативам, которые гарантируют сохранение уровня, а в перспективе - рост объемов производства сельскохозяйственной продукции, создание рабочих мест. При этом все формы кооперации будут иметь преимущественное право на государственную поддержку.
   Развитие сельхозкооперативов в Кыргызской Республике находится на начальном этапе и играет важную роль в укреплении экономики, конкурентоспособности, улучшении условий хозяйствования и создании стимулов для роста товарной продукции.         
 Разработанная методика расчета индикатора ЦУР 2.3.2.a  будет служить информационной базой для реализации социально-экономической политики в сфере обеспечения продовольственной безопасности страны, позволит обеспечить продовольственную безопасность Кыргызстана, как важнейшую составную часть национальной    стратегией устойчивого развития, создавать условия для динамичного развития отечественного агропромышленного сектора, улучшения благосостояния населения.</t>
   </si>
@@ -137,9 +137,8 @@
 - форма №29(годовая) «О сборе урожая сельскохозяйственных культур со всех земель и с орошаемых земель».</t>
   </si>
   <si>
-    <t xml:space="preserve"> - сельскохозяйственные кооперативы (юридические лица) самостоятельно представляют отчеты по государственным формам статистической отчетности сельского хозяйства в статистические органы по территории.
-  - сбор информации по отрасли растениеводства:
-- сбор информации по отрасли животноводства (поголовье скота и их продукция):</t>
+    <t>сельскохозяйственные кооперативы (юридические лица) самостоятельно представляют отчеты по государственным формам статистической отчетности сельского хозяйства в статистические органы по территории.
+ сбор информации по отрасли растениеводства сбор информации по отрасли животноводства (поголовье скота и их продукция)</t>
   </si>
   <si>
     <t>Расчет дополнительного национального индикатора ЦУР 2.3.2.a  Доля произведенной продукции сельскохозяйственными кооперативами в общем объеме произведенной продукции в республики рассчитывается по формуле:
@@ -158,8 +157,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,13 +197,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -220,7 +212,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -243,29 +235,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -285,38 +260,14 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 2 2" xfId="3"/>
-    <cellStyle name="Обычный 2 3" xfId="5"/>
-    <cellStyle name="Обычный 2 4" xfId="2"/>
-    <cellStyle name="Обычный 3" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -332,9 +283,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -372,9 +323,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -409,7 +360,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -444,7 +395,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -617,7 +568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -652,7 +603,7 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -666,7 +617,7 @@
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -674,7 +625,7 @@
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>30</v>
       </c>
     </row>
@@ -682,7 +633,7 @@
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -690,7 +641,7 @@
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>32</v>
       </c>
     </row>
@@ -698,7 +649,7 @@
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -712,23 +663,23 @@
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="234.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="7" t="s">
         <v>36</v>
       </c>
     </row>
@@ -742,7 +693,7 @@
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>37</v>
       </c>
     </row>
@@ -750,7 +701,7 @@
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -760,15 +711,15 @@
       </c>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
@@ -778,7 +729,7 @@
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>40</v>
       </c>
     </row>
